--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -956,7 +956,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2452,7 +2452,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2948,7 +2948,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3692,7 +3692,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3754,7 +3754,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4498,7 +4498,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4560,7 +4560,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6110,7 +6110,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6172,7 +6172,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6358,7 +6358,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6668,7 +6668,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -6978,7 +6978,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7350,7 +7350,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7536,7 +7536,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8094,7 +8094,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8156,7 +8156,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8528,7 +8528,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8838,7 +8838,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -8962,7 +8962,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9024,7 +9024,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9210,7 +9210,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9272,7 +9272,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -9892,7 +9892,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10636,7 +10636,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10822,7 +10822,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10884,7 +10884,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11256,7 +11256,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11876,7 +11876,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12000,7 +12000,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12186,7 +12186,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12434,7 +12434,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13426,7 +13426,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13860,7 +13860,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -13984,7 +13984,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14108,7 +14108,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14356,7 +14356,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14480,7 +14480,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14604,7 +14604,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14728,7 +14728,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14852,7 +14852,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15100,7 +15100,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15286,7 +15286,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15348,7 +15348,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15472,7 +15472,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15782,7 +15782,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15844,7 +15844,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -15968,7 +15968,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16030,7 +16030,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16154,7 +16154,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16340,7 +16340,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16402,7 +16402,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16588,7 +16588,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16712,7 +16712,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -16898,7 +16898,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17146,7 +17146,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17270,7 +17270,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17332,7 +17332,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17394,7 +17394,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17518,7 +17518,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17642,7 +17642,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17704,7 +17704,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17766,7 +17766,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17828,7 +17828,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -17890,7 +17890,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18200,7 +18200,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18262,7 +18262,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18324,7 +18324,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18386,7 +18386,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18696,7 +18696,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18758,7 +18758,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18820,7 +18820,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19006,7 +19006,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19068,7 +19068,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19192,7 +19192,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19254,7 +19254,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19378,7 +19378,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19440,7 +19440,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19626,7 +19626,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19688,7 +19688,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -19936,7 +19936,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -19998,7 +19998,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20122,7 +20122,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20184,7 +20184,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20556,7 +20556,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20618,7 +20618,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20680,7 +20680,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20742,7 +20742,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -20990,7 +20990,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21176,7 +21176,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21238,7 +21238,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21300,7 +21300,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21362,7 +21362,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21424,7 +21424,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21486,7 +21486,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21548,7 +21548,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21610,7 +21610,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21672,7 +21672,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21796,7 +21796,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21858,7 +21858,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -21920,7 +21920,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -21982,7 +21982,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22044,7 +22044,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22168,7 +22168,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22230,7 +22230,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22292,7 +22292,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22354,7 +22354,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22478,7 +22478,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22540,7 +22540,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -23339,7 +23339,7 @@
           <t>B | 390呎 (2房)
 $861万
 $22,085/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -23347,7 +23347,7 @@
           <t>C | 388呎 (2房)
 $847万
 $21,830/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E5" s="21" t="inlineStr">
@@ -23355,7 +23355,7 @@
           <t>D | 389呎 (2房)
 $841万
 $21,620/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -23363,7 +23363,7 @@
           <t>E | 393呎 (2房)
 $841万
 $21,400/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -23371,7 +23371,7 @@
           <t>F | 399呎 (2房)
 $860万
 $21,541/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr">
@@ -23379,7 +23379,7 @@
           <t>G | 398呎 (2房)
 $830万
 $20,857/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="I5" s="21" t="inlineStr">
@@ -23387,7 +23387,7 @@
           <t>H | 399呎 (2房)
 $824万
 $20,652/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr">
@@ -23395,7 +23395,7 @@
           <t>J | 339呎 (2房)
 $756万
 $22,315/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -23403,7 +23403,7 @@
           <t>K | 339呎 (2房)
 $764万
 $22,540/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -23411,7 +23411,7 @@
           <t>L | 339呎 (2房)
 $780万
 $23,017/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -23419,7 +23419,7 @@
           <t>M | 339呎 (2房)
 $740万
 $21,818/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="N5" s="21" t="inlineStr">
@@ -23427,7 +23427,7 @@
           <t>N | 339呎 (2房)
 $726万
 $21,427/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -23435,7 +23435,7 @@
           <t>P | 343呎 (2房)
 $721万
 $21,017/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P5" s="20" t="inlineStr">
@@ -23458,7 +23458,7 @@
           <t>A | 642呎 (3房)
 $1400万
 $21,805/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C6" s="21" t="inlineStr">
@@ -23466,7 +23466,7 @@
           <t>B | 390呎 (2房)
 $857万
 $21,968/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr">
@@ -23474,7 +23474,7 @@
           <t>C | 388呎 (2房)
 $841万
 $21,678/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -23482,7 +23482,7 @@
           <t>D | 389呎 (2房)
 $835万
 $21,463/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -23490,7 +23490,7 @@
           <t>E | 393呎 (2房)
 $853万
 $21,714/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -23498,7 +23498,7 @@
           <t>F | 399呎 (2房)
 $835万
 $20,930/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr">
@@ -23506,7 +23506,7 @@
           <t>G | 398呎 (2房)
 $820万
 $20,614/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -23514,7 +23514,7 @@
           <t>H | 399呎 (2房)
 $814万
 $20,410/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr">
@@ -23522,7 +23522,7 @@
           <t>J | 339呎 (2房)
 $745万
 $21,969/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="K6" s="21" t="inlineStr">
@@ -23530,7 +23530,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L6" s="21" t="inlineStr">
@@ -23538,7 +23538,7 @@
           <t>L | 339呎 (2房)
 $770万
 $22,707/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M6" s="21" t="inlineStr">
@@ -23546,7 +23546,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,510/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -23554,7 +23554,7 @@
           <t>N | 339呎 (2房)
 $720万
 $21,225/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -23562,7 +23562,7 @@
           <t>P | 343呎 (2房)
 $714万
 $20,829/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
@@ -23570,7 +23570,7 @@
           <t>Q | 435呎 (2房)
 $927万
 $21,321/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -23585,7 +23585,7 @@
           <t>A | 642呎 (3房)
 $1387万
 $21,600/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C7" s="21" t="inlineStr">
@@ -23593,7 +23593,7 @@
           <t>B | 390呎 (2房)
 $852万
 $21,858/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -23601,7 +23601,7 @@
           <t>C | 388呎 (2房)
 $853万
 $21,984/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E7" s="21" t="inlineStr">
@@ -23609,7 +23609,7 @@
           <t>D | 389呎 (2房)
 $849万
 $21,828/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -23617,7 +23617,7 @@
           <t>E | 393呎 (2房)
 $829万
 $21,085/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -23625,7 +23625,7 @@
           <t>F | 399呎 (2房)
 $827万
 $20,722/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -23633,7 +23633,7 @@
           <t>G | 398呎 (2房)
 $812万
 $20,411/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -23641,7 +23641,7 @@
           <t>H | 399呎 (2房)
 $803万
 $20,129/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -23649,7 +23649,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,681/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K7" s="21" t="inlineStr">
@@ -23657,7 +23657,7 @@
           <t>K | 339呎 (2房)
 $776万
 $22,904/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="L7" s="21" t="inlineStr">
@@ -23665,7 +23665,7 @@
           <t>L | 339呎 (2房)
 $747万
 $22,033/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M7" s="21" t="inlineStr">
@@ -23673,7 +23673,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,303/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -23681,7 +23681,7 @@
           <t>N | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -23689,7 +23689,7 @@
           <t>P | 343呎 (2房)
 $709万
 $20,670/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P7" s="21" t="inlineStr">
@@ -23697,7 +23697,7 @@
           <t>Q | 435呎 (2房)
 $919万
 $21,135/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -23712,7 +23712,7 @@
           <t>A | 642呎 (3房)
 $1377万
 $21,444/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C8" s="21" t="inlineStr">
@@ -23720,7 +23720,7 @@
           <t>B | 390呎 (2房)
 $848万
 $21,749/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D8" s="21" t="inlineStr">
@@ -23728,7 +23728,7 @@
           <t>C | 388呎 (2房)
 $827万
 $21,324/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -23736,7 +23736,7 @@
           <t>D | 389呎 (2房)
 $827万
 $21,271/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -23744,7 +23744,7 @@
           <t>E | 393呎 (2房)
 $825万
 $20,997/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -23752,7 +23752,7 @@
           <t>F | 399呎 (2房)
 $818万
 $20,508/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -23760,7 +23760,7 @@
           <t>G | 398呎 (2房)
 $802万
 $20,159/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I8" s="21" t="inlineStr">
@@ -23768,7 +23768,7 @@
           <t>H | 399呎 (2房)
 $795万
 $19,922/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr">
@@ -23776,7 +23776,7 @@
           <t>J | 339呎 (2房)
 $725万
 $21,378/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="K8" s="21" t="inlineStr">
@@ -23784,7 +23784,7 @@
           <t>K | 339呎 (2房)
 $726万
 $21,408/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -23792,7 +23792,7 @@
           <t>L | 339呎 (2房)
 $740万
 $21,827/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M8" s="21" t="inlineStr">
@@ -23800,7 +23800,7 @@
           <t>M | 339呎 (2房)
 $731万
 $21,563/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N8" s="21" t="inlineStr">
@@ -23808,7 +23808,7 @@
           <t>N | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O8" s="21" t="inlineStr">
@@ -23816,7 +23816,7 @@
           <t>P | 343呎 (2房)
 $720万
 $20,986/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -23824,7 +23824,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,955/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
     </row>
@@ -23839,7 +23839,7 @@
           <t>A | 642呎 (3房)
 $1367万
 $21,296/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr">
@@ -23847,7 +23847,7 @@
           <t>B | 390呎 (2房)
 $844万
 $21,637/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D9" s="21" t="inlineStr">
@@ -23855,7 +23855,7 @@
           <t>C | 388呎 (2房)
 $821万
 $21,153/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -23863,7 +23863,7 @@
           <t>D | 389呎 (2房)
 $823万
 $21,161/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -23871,7 +23871,7 @@
           <t>E | 393呎 (2房)
 $819万
 $20,828/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -23879,7 +23879,7 @@
           <t>F | 399呎 (2房)
 $856万
 $21,462/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -23887,7 +23887,7 @@
           <t>G | 398呎 (2房)
 $796万
 $19,997/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -23895,7 +23895,7 @@
           <t>H | 399呎 (2房)
 $788万
 $19,758/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr">
@@ -23903,7 +23903,7 @@
           <t>J | 339呎 (2房)
 $733万
 $21,623/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="K9" s="21" t="inlineStr">
@@ -23911,7 +23911,7 @@
           <t>K | 339呎 (2房)
 $715万
 $21,086/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -23919,7 +23919,7 @@
           <t>L | 339呎 (2房)
 $732万
 $21,582/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M9" s="21" t="inlineStr">
@@ -23927,7 +23927,7 @@
           <t>M | 339呎 (2房)
 $725万
 $21,398/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N9" s="21" t="inlineStr">
@@ -23935,7 +23935,7 @@
           <t>N | 339呎 (2房)
 $698万
 $20,594/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O9" s="21" t="inlineStr">
@@ -23943,7 +23943,7 @@
           <t>P | 343呎 (2房)
 $735万
 $21,439/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -23951,7 +23951,7 @@
           <t>Q | 435呎 (2房)
 $905万
 $20,809/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -23966,7 +23966,7 @@
           <t>A | 642呎 (3房)
 $1359万
 $21,165/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr">
@@ -23974,7 +23974,7 @@
           <t>B | 390呎 (2房)
 $838万
 $21,483/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -23982,7 +23982,7 @@
           <t>C | 388呎 (2房)
 $860万
 $22,176/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -23990,7 +23990,7 @@
           <t>D | 389呎 (2房)
 $864万
 $22,223/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -23998,7 +23998,7 @@
           <t>E | 393呎 (2房)
 $857万
 $21,794/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -24006,7 +24006,7 @@
           <t>F | 399呎 (2房)
 $852万
 $21,348/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -24014,7 +24014,7 @@
           <t>G | 398呎 (2房)
 $789万
 $19,835/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -24022,7 +24022,7 @@
           <t>H | 399呎 (2房)
 $799万
 $20,031/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr">
@@ -24030,7 +24030,7 @@
           <t>J | 339呎 (2房)
 $713万
 $21,024/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K10" s="21" t="inlineStr">
@@ -24038,7 +24038,7 @@
           <t>K | 339呎 (2房)
 $709万
 $20,917/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L10" s="21" t="inlineStr">
@@ -24046,7 +24046,7 @@
           <t>L | 339呎 (2房)
 $766万
 $22,606/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M10" s="21" t="inlineStr">
@@ -24054,7 +24054,7 @@
           <t>M | 339呎 (2房)
 $722万
 $21,286/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N10" s="21" t="inlineStr">
@@ -24062,7 +24062,7 @@
           <t>N | 339呎 (2房)
 $694万
 $20,468/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O10" s="21" t="inlineStr">
@@ -24070,7 +24070,7 @@
           <t>P | 343呎 (2房)
 $688万
 $20,065/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P10" s="21" t="inlineStr">
@@ -24078,7 +24078,7 @@
           <t>Q | 435呎 (2房)
 $898万
 $20,639/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -24093,7 +24093,7 @@
           <t>A | 642呎 (3房)
 $1350万
 $21,035/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C11" s="21" t="inlineStr">
@@ -24101,7 +24101,7 @@
           <t>B | 390呎 (2房)
 $849万
 $21,778/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
@@ -24109,7 +24109,7 @@
           <t>C | 388呎 (2房)
 $811万
 $20,909/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -24117,7 +24117,7 @@
           <t>D | 389呎 (2房)
 $814万
 $20,914/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -24125,7 +24125,7 @@
           <t>E | 393呎 (2房)
 $809万
 $20,592/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -24133,7 +24133,7 @@
           <t>F | 399呎 (2房)
 $845万
 $21,180/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -24141,7 +24141,7 @@
           <t>G | 398呎 (2房)
 $779万
 $19,581/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -24149,7 +24149,7 @@
           <t>H | 399呎 (2房)
 $775万
 $19,420/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr">
@@ -24157,7 +24157,7 @@
           <t>J | 339呎 (2房)
 $709万
 $20,914/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K11" s="21" t="inlineStr">
@@ -24165,7 +24165,7 @@
           <t>K | 339呎 (2房)
 $747万
 $22,029/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L11" s="21" t="inlineStr">
@@ -24173,7 +24173,7 @@
           <t>L | 339呎 (2房)
 $762万
 $22,488/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M11" s="21" t="inlineStr">
@@ -24181,7 +24181,7 @@
           <t>M | 339呎 (2房)
 $742万
 $21,876/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N11" s="21" t="inlineStr">
@@ -24189,7 +24189,7 @@
           <t>N | 339呎 (2房)
 $705万
 $20,808/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="O11" s="21" t="inlineStr">
@@ -24197,7 +24197,7 @@
           <t>P | 343呎 (2房)
 $686万
 $19,999/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="P11" s="21" t="inlineStr">
@@ -24205,7 +24205,7 @@
           <t>Q | 435呎 (2房)
 $891万
 $20,489/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24220,7 @@
           <t>A | 642呎 (3房)
 $1340万
 $20,866/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr">
@@ -24228,7 +24228,7 @@
           <t>B | 390呎 (2房)
 $825万
 $21,142/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -24236,7 +24236,7 @@
           <t>C | 388呎 (2房)
 $806万
 $20,777/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -24244,7 +24244,7 @@
           <t>D | 389呎 (2房)
 $852万
 $21,905/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -24252,7 +24252,7 @@
           <t>E | 393呎 (2房)
 $802万
 $20,416/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -24260,7 +24260,7 @@
           <t>F | 399呎 (2房)
 $795万
 $19,931/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -24268,7 +24268,7 @@
           <t>G | 398呎 (2房)
 $769万
 $19,327/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -24276,7 +24276,7 @@
           <t>H | 399呎 (2房)
 $811万
 $20,336/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr">
@@ -24284,7 +24284,7 @@
           <t>J | 339呎 (2房)
 $703万
 $20,745/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="K12" s="21" t="inlineStr">
@@ -24292,7 +24292,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L12" s="21" t="inlineStr">
@@ -24300,7 +24300,7 @@
           <t>L | 339呎 (2房)
 $718万
 $21,185/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="M12" s="21" t="inlineStr">
@@ -24308,7 +24308,7 @@
           <t>M | 339呎 (2房)
 $738万
 $21,757/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N12" s="21" t="inlineStr">
@@ -24316,7 +24316,7 @@
           <t>N | 339呎 (2房)
 $686万
 $20,251/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O12" s="21" t="inlineStr">
@@ -24324,7 +24324,7 @@
           <t>P | 343呎 (2房)
 $684万
 $19,927/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P12" s="21" t="inlineStr">
@@ -24332,7 +24332,7 @@
           <t>Q | 435呎 (2房)
 $888万
 $20,420/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -24347,7 +24347,7 @@
           <t>A | 642呎 (3房)
 $1345万
 $20,945/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr">
@@ -24355,7 +24355,7 @@
           <t>B | 390呎 (2房)
 $818万
 $20,972/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="D13" s="21" t="inlineStr">
@@ -24363,7 +24363,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,597/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -24371,7 +24371,7 @@
           <t>D | 389呎 (2房)
 $845万
 $21,712/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -24379,7 +24379,7 @@
           <t>E | 393呎 (2房)
 $796万
 $20,242/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -24387,7 +24387,7 @@
           <t>F | 399呎 (2房)
 $786万
 $19,696/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -24395,7 +24395,7 @@
           <t>G | 398呎 (2房)
 $741万
 $18,621/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -24403,7 +24403,7 @@
           <t>H | 399呎 (2房)
 $805万
 $20,172/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr">
@@ -24411,7 +24411,7 @@
           <t>J | 339呎 (2房)
 $735万
 $21,686/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K13" s="21" t="inlineStr">
@@ -24419,7 +24419,7 @@
           <t>K | 339呎 (2房)
 $695万
 $20,503/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="L13" s="21" t="inlineStr">
@@ -24427,7 +24427,7 @@
           <t>L | 339呎 (2房)
 $715万
 $21,091/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M13" s="21" t="inlineStr">
@@ -24435,7 +24435,7 @@
           <t>M | 339呎 (2房)
 $734万
 $21,641/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N13" s="21" t="inlineStr">
@@ -24443,7 +24443,7 @@
           <t>N | 339呎 (2房)
 $699万
 $20,605/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O13" s="21" t="inlineStr">
@@ -24451,7 +24451,7 @@
           <t>P | 343呎 (2房)
 $719万
 $20,952/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="P13" s="21" t="inlineStr">
@@ -24459,7 +24459,7 @@
           <t>Q | 435呎 (2房)
 $885万
 $20,348/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -24474,7 +24474,7 @@
           <t>A | 642呎 (3房)
 $1320万
 $20,567/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -24482,7 +24482,7 @@
           <t>B | 390呎 (2房)
 $810万
 $20,778/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D14" s="21" t="inlineStr">
@@ -24490,7 +24490,7 @@
           <t>C | 388呎 (2房)
 $792万
 $20,419/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -24498,7 +24498,7 @@
           <t>D | 389呎 (2房)
 $810万
 $20,835/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -24506,7 +24506,7 @@
           <t>E | 393呎 (2房)
 $798万
 $20,306/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -24514,7 +24514,7 @@
           <t>F | 399呎 (2房)
 $779万
 $19,518/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -24522,7 +24522,7 @@
           <t>G | 398呎 (2房)
 $738万
 $18,554/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -24538,7 +24538,7 @@
           <t>J | 339呎 (2房)
 $690万
 $20,369/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K14" s="21" t="inlineStr">
@@ -24546,7 +24546,7 @@
           <t>K | 339呎 (2房)
 $686万
 $20,240/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L14" s="21" t="inlineStr">
@@ -24554,7 +24554,7 @@
           <t>L | 339呎 (2房)
 $712万
 $20,997/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="M14" s="21" t="inlineStr">
@@ -24562,7 +24562,7 @@
           <t>M | 339呎 (2房)
 $729万
 $21,505/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N14" s="21" t="inlineStr">
@@ -24570,7 +24570,7 @@
           <t>N | 339呎 (2房)
 $681万
 $20,076/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="O14" s="21" t="inlineStr">
@@ -24578,7 +24578,7 @@
           <t>P | 343呎 (2房)
 $676万
 $19,701/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P14" s="21" t="inlineStr">
@@ -24586,7 +24586,7 @@
           <t>Q | 435呎 (2房)
 $882万
 $20,277/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
     </row>
@@ -24601,7 +24601,7 @@
           <t>A | 642呎 (3房)
 $1301万
 $20,270/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr">
@@ -24609,7 +24609,7 @@
           <t>B | 390呎 (2房)
 $802万
 $20,564/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="D15" s="21" t="inlineStr">
@@ -24617,7 +24617,7 @@
           <t>C | 388呎 (2房)
 $786万
 $20,245/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -24625,7 +24625,7 @@
           <t>D | 389呎 (2房)
 $803万
 $20,637/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -24633,7 +24633,7 @@
           <t>E | 393呎 (2房)
 $774万
 $19,707/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -24641,7 +24641,7 @@
           <t>F | 399呎 (2房)
 $772万
 $19,338/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -24649,7 +24649,7 @@
           <t>G | 398呎 (2房)
 $736万
 $18,490/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -24665,7 +24665,7 @@
           <t>J | 339呎 (2房)
 $683万
 $20,146/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K15" s="21" t="inlineStr">
@@ -24673,7 +24673,7 @@
           <t>K | 339呎 (2房)
 $677万
 $19,974/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="L15" s="21" t="inlineStr">
@@ -24681,7 +24681,7 @@
           <t>L | 339呎 (2房)
 $704万
 $20,771/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M15" s="21" t="inlineStr">
@@ -24689,7 +24689,7 @@
           <t>M | 339呎 (2房)
 $726万
 $21,409/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="N15" s="21" t="inlineStr">
@@ -24697,7 +24697,7 @@
           <t>N | 339呎 (2房)
 $675万
 $19,912/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="O15" s="21" t="inlineStr">
@@ -24705,7 +24705,7 @@
           <t>P | 343呎 (2房)
 $673万
 $19,633/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="P15" s="21" t="inlineStr">
@@ -24713,7 +24713,7 @@
           <t>Q | 435呎 (2房)
 $879万
 $20,208/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -24728,7 +24728,7 @@
           <t>A | 642呎 (3房)
 $1251万
 $19,491/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>B | 390呎 (2房)
 $796万
 $20,403/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D16" s="21" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>C | 388呎 (2房)
 $799万
 $20,585/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>D | 389呎 (2房)
 $778万
 $19,999/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>E | 393呎 (2房)
 $763万
 $19,422/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>F | 399呎 (2房)
 $766万
 $19,187/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -24776,7 +24776,7 @@
           <t>G | 398呎 (2房)
 $732万
 $18,396/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -24792,7 +24792,7 @@
           <t>J | 339呎 (2房)
 $689万
 $20,331/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K16" s="21" t="inlineStr">
@@ -24800,7 +24800,7 @@
           <t>K | 339呎 (2房)
 $712万
 $21,009/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L16" s="21" t="inlineStr">
@@ -24808,7 +24808,7 @@
           <t>L | 339呎 (2房)
 $699万
 $20,608/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M16" s="21" t="inlineStr">
@@ -24816,7 +24816,7 @@
           <t>M | 339呎 (2房)
 $700万
 $20,635/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="N16" s="21" t="inlineStr">
@@ -24824,7 +24824,7 @@
           <t>N | 339呎 (2房)
 $666万
 $19,660/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="O16" s="21" t="inlineStr">
@@ -24832,7 +24832,7 @@
           <t>P | 343呎 (2房)
 $668万
 $19,476/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P16" s="21" t="inlineStr">
@@ -24840,7 +24840,7 @@
           <t>Q | 435呎 (2房)
 $876万
 $20,143/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -24855,7 +24855,7 @@
           <t>A | 642呎 (3房)
 $1231万
 $19,178/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr">
@@ -24863,7 +24863,7 @@
           <t>B | 390呎 (2房)
 $832万
 $21,336/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D17" s="21" t="inlineStr">
@@ -24871,7 +24871,7 @@
           <t>C | 388呎 (2房)
 $776万
 $20,001/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -24879,7 +24879,7 @@
           <t>D | 389呎 (2房)
 $788万
 $20,250/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -24887,7 +24887,7 @@
           <t>E | 393呎 (2房)
 $751万
 $19,105/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -24895,7 +24895,7 @@
           <t>F | 399呎 (2房)
 $797万
 $19,963/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -24903,7 +24903,7 @@
           <t>G | 398呎 (2房)
 $727万
 $18,264/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -24919,7 +24919,7 @@
           <t>J | 339呎 (2房)
 $686万
 $20,249/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="K17" s="21" t="inlineStr">
@@ -24927,7 +24927,7 @@
           <t>K | 339呎 (2房)
 $687万
 $20,273/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L17" s="21" t="inlineStr">
@@ -24935,7 +24935,7 @@
           <t>L | 339呎 (2房)
 $693万
 $20,452/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M17" s="21" t="inlineStr">
@@ -24943,7 +24943,7 @@
           <t>M | 339呎 (2房)
 $719万
 $21,216/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N17" s="21" t="inlineStr">
@@ -24951,7 +24951,7 @@
           <t>N | 339呎 (2房)
 $661万
 $19,486/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="O17" s="21" t="inlineStr">
@@ -24959,7 +24959,7 @@
           <t>P | 343呎 (2房)
 $662万
 $19,301/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P17" s="21" t="inlineStr">
@@ -24967,7 +24967,7 @@
           <t>Q | 435呎 (2房)
 $921万
 $21,166/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
           <t>A | 642呎 (3房)
 $1215万
 $18,927/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr">
@@ -24990,7 +24990,7 @@
           <t>B | 390呎 (2房)
 $824万
 $21,125/呎
-(26年-04月-29日)</t>
+(26年-04月-30日)</t>
         </is>
       </c>
       <c r="D18" s="21" t="inlineStr">
@@ -24998,7 +24998,7 @@
           <t>C | 388呎 (2房)
 $771万
 $19,877/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -25006,7 +25006,7 @@
           <t>D | 389呎 (2房)
 $808万
 $20,769/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -25014,7 +25014,7 @@
           <t>E | 393呎 (2房)
 $738万
 $18,788/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -25022,7 +25022,7 @@
           <t>F | 399呎 (2房)
 $745万
 $18,674/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -25030,7 +25030,7 @@
           <t>G | 398呎 (2房)
 $764万
 $19,200/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25046,7 +25046,7 @@
           <t>J | 339呎 (2房)
 $669万
 $19,741/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K18" s="21" t="inlineStr">
@@ -25054,7 +25054,7 @@
           <t>K | 339呎 (2房)
 $670万
 $19,765/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L18" s="21" t="inlineStr">
@@ -25062,7 +25062,7 @@
           <t>L | 339呎 (2房)
 $689万
 $20,323/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="M18" s="21" t="inlineStr">
@@ -25070,7 +25070,7 @@
           <t>M | 339呎 (2房)
 $713万
 $21,038/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N18" s="21" t="inlineStr">
@@ -25078,7 +25078,7 @@
           <t>N | 339呎 (2房)
 $658万
 $19,416/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="O18" s="21" t="inlineStr">
@@ -25086,7 +25086,7 @@
           <t>P | 343呎 (2房)
 $660万
 $19,237/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="P18" s="21" t="inlineStr">
@@ -25094,7 +25094,7 @@
           <t>Q | 435呎 (2房)
 $870万
 $19,993/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
     </row>
@@ -25109,7 +25109,7 @@
           <t>A | 642呎 (3房)
 $1211万
 $18,860/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr">
@@ -25117,7 +25117,7 @@
           <t>B | 390呎 (2房)
 $777万
 $19,917/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -25125,7 +25125,7 @@
           <t>C | 388呎 (2房)
 $768万
 $19,788/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -25133,7 +25133,7 @@
           <t>D | 389呎 (2房)
 $762万
 $19,580/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -25141,7 +25141,7 @@
           <t>E | 393呎 (2房)
 $761万
 $19,368/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -25149,7 +25149,7 @@
           <t>F | 399呎 (2房)
 $776万
 $19,443/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -25157,7 +25157,7 @@
           <t>G | 398呎 (2房)
 $722万
 $18,136/呎
-(26年-04月-24日)</t>
+(26年-04月-25日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>J | 339呎 (2房)
 $667万
 $19,671/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K19" s="21" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>K | 339呎 (2房)
 $704万
 $20,777/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="L19" s="21" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>L | 339呎 (2房)
 $722万
 $21,301/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M19" s="21" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>M | 339呎 (2房)
 $709万
 $20,905/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="N19" s="21" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>N | 339呎 (2房)
 $656万
 $19,349/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="O19" s="21" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>P | 343呎 (2房)
 $658万
 $19,171/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="P19" s="21" t="inlineStr">
@@ -25221,7 +25221,7 @@
           <t>Q | 435呎 (2房)
 $867万
 $19,924/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -25236,7 +25236,7 @@
           <t>A | 642呎 (3房)
 $1207万
 $18,794/呎
-(26年-04月-24日)</t>
+(26年-04月-25日)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr">
@@ -25244,7 +25244,7 @@
           <t>B | 390呎 (2房)
 $790万
 $20,245/呎
-(26年-05月-27日)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="D20" s="21" t="inlineStr">
@@ -25252,7 +25252,7 @@
           <t>C | 388呎 (2房)
 $761万
 $19,621/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -25260,7 +25260,7 @@
           <t>D | 389呎 (2房)
 $799万
 $20,545/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -25268,7 +25268,7 @@
           <t>E | 393呎 (2房)
 $708万
 $18,024/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -25276,7 +25276,7 @@
           <t>F | 399呎 (2房)
 $718万
 $18,004/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -25284,7 +25284,7 @@
           <t>G | 398呎 (2房)
 $759万
 $19,062/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25300,7 +25300,7 @@
           <t>J | 339呎 (2房)
 $664万
 $19,596/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K20" s="21" t="inlineStr">
@@ -25308,7 +25308,7 @@
           <t>K | 339呎 (2房)
 $665万
 $19,623/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="L20" s="21" t="inlineStr">
@@ -25316,7 +25316,7 @@
           <t>L | 339呎 (2房)
 $680万
 $20,063/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M20" s="21" t="inlineStr">
@@ -25324,7 +25324,7 @@
           <t>M | 339呎 (2房)
 $668万
 $19,706/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N20" s="21" t="inlineStr">
@@ -25332,7 +25332,7 @@
           <t>N | 339呎 (2房)
 $654万
 $19,282/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O20" s="21" t="inlineStr">
@@ -25340,10 +25340,772 @@
           <t>P | 343呎 (2房)
 $655万
 $19,102/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="P20" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$864万
+$19,853/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1229万
+$19,137/呎
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="P20" s="21" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$786万
+$20,155/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$757万
+$19,516/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$752万
+$19,330/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$706万
+$17,961/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$716万
+$17,940/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$717万
+$18,006/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="I21" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$781万
+$19,564/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$662万
+$19,526/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="K21" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$676万
+$19,944/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$676万
+$19,953/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="M21" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$666万
+$19,636/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N21" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$653万
+$19,250/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="O21" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$654万
+$19,078/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="P21" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$861万
+$19,783/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1198万
+$18,661/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$765万
+$19,612/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$796万
+$20,514/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$749万
+$19,243/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$703万
+$17,894/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$713万
+$17,876/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$730万
+$18,336/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$779万
+$19,531/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J22" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$660万
+$19,456/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="K22" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$656万
+$19,365/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="L22" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$685万
+$20,196/呎
+(26年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="M22" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$663万
+$19,563/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$651万
+$19,201/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$653万
+$19,028/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+      <c r="P22" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$905万
+$20,793/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1194万
+$18,594/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$802万
+$20,576/呎
+(26年-05月-28日)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$793万
+$20,439/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$746万
+$19,171/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$701万
+$17,830/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$750万
+$18,791/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$711万
+$17,875/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$778万
+$19,501/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J23" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$693万
+$20,449/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="K23" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$690万
+$20,353/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$664万
+$19,596/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="M23" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$661万
+$19,494/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N23" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$650万
+$19,172/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="O23" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$652万
+$18,999/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="P23" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$854万
+$19,639/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1218万
+$18,965/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$758万
+$19,429/呎
+(26年-05月-29日)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$789万
+$20,338/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$758万
+$19,496/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$699万
+$17,792/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$709万
+$17,776/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$710万
+$17,841/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$776万
+$19,441/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$670万
+$19,768/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="K24" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$667万
+$19,675/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="L24" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$660万
+$19,464/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="M24" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$659万
+$19,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N24" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$646万
+$19,064/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$651万
+$18,969/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="P24" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$899万
+$20,668/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1187万
+$18,495/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$755万
+$19,362/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$746万
+$19,215/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$756万
+$19,432/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$698万
+$17,765/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$708万
+$17,748/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$709万
+$17,811/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$772万
+$19,358/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$688万
+$20,301/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="K25" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$649万
+$19,153/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$656万
+$19,365/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="M25" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$656万
+$19,349/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N25" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$645万
+$19,035/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="O25" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$647万
+$18,863/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="P25" s="21" t="inlineStr">
+        <is>
+          <t>Q | 435呎 (2房)
+$848万
+$19,497/呎
+(26年-05月-27日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>A | 642呎 (3房)
+$1185万
+$18,461/呎
+(26年-04月-25日)</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>B | 390呎 (2房)
+$752万
+$19,292/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
+        <is>
+          <t>C | 388呎 (2房)
+$741万
+$19,089/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 389呎 (2房)
+$735万
+$18,888/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 393呎 (2房)
+$697万
+$17,734/呎
+(26年-05月-20日)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 399呎 (2房)
+$707万
+$17,719/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
+        <is>
+          <t>G | 398呎 (2房)
+$746万
+$18,756/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
+        <is>
+          <t>H | 399呎 (2房)
+$698万
+$17,481/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="J26" s="21" t="inlineStr">
+        <is>
+          <t>J | 339呎 (2房)
+$650万
+$19,169/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="K26" s="21" t="inlineStr">
+        <is>
+          <t>K | 339呎 (2房)
+$661万
+$19,500/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+      <c r="L26" s="21" t="inlineStr">
+        <is>
+          <t>L | 339呎 (2房)
+$654万
+$19,292/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="M26" s="21" t="inlineStr">
+        <is>
+          <t>M | 339呎 (2房)
+$654万
+$19,279/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="N26" s="21" t="inlineStr">
+        <is>
+          <t>N | 339呎 (2房)
+$643万
+$18,968/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t>P | 343呎 (2房)
+$645万
+$18,797/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="P26" s="21" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 $864万
@@ -25352,768 +26114,6 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1229万
-$19,137/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$786万
-$20,155/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$757万
-$19,516/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$752万
-$19,330/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$706万
-$17,961/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$716万
-$17,940/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$717万
-$18,006/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="I21" s="22" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$781万
-$19,564/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$662万
-$19,526/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="K21" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$676万
-$19,944/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="L21" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$676万
-$19,953/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="M21" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$666万
-$19,636/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$653万
-$19,250/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="O21" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$654万
-$19,078/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="P21" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$861万
-$19,783/呎
-(26年-05月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1198万
-$18,661/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C22" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$765万
-$19,612/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$796万
-$20,514/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$749万
-$19,243/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$703万
-$17,894/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$713万
-$17,876/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$730万
-$18,336/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$779万
-$19,531/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J22" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$660万
-$19,456/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="K22" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$656万
-$19,365/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$685万
-$20,196/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="M22" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$663万
-$19,563/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$651万
-$19,201/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="O22" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$653万
-$19,028/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="P22" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$905万
-$20,793/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1194万
-$18,594/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="C23" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$802万
-$20,576/呎
-(26年-05月-27日)</t>
-        </is>
-      </c>
-      <c r="D23" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$793万
-$20,439/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$746万
-$19,171/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$701万
-$17,830/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$750万
-$18,791/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$711万
-$17,875/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$778万
-$19,501/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J23" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$693万
-$20,449/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="K23" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$690万
-$20,353/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="L23" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$664万
-$19,596/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="M23" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$661万
-$19,494/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N23" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$650万
-$19,172/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="O23" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$652万
-$18,999/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="P23" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$854万
-$19,639/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1218万
-$18,965/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="C24" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$758万
-$19,429/呎
-(26年-05月-28日)</t>
-        </is>
-      </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$789万
-$20,338/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$758万
-$19,496/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$699万
-$17,792/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$709万
-$17,776/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$710万
-$17,841/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$776万
-$19,441/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J24" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$670万
-$19,768/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="K24" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$667万
-$19,675/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="L24" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$660万
-$19,464/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="M24" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$659万
-$19,453/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N24" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$646万
-$19,064/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="O24" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$651万
-$18,969/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="P24" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$899万
-$20,668/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1187万
-$18,495/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="C25" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$755万
-$19,362/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$746万
-$19,215/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$756万
-$19,432/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$698万
-$17,765/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$708万
-$17,748/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$709万
-$17,811/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$772万
-$19,358/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="J25" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$688万
-$20,301/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="K25" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$649万
-$19,153/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$656万
-$19,365/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="M25" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$656万
-$19,349/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N25" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$645万
-$19,035/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="O25" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$647万
-$18,863/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="P25" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$848万
-$19,497/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>A | 642呎 (3房)
-$1185万
-$18,461/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="C26" s="21" t="inlineStr">
-        <is>
-          <t>B | 390呎 (2房)
-$752万
-$19,292/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>C | 388呎 (2房)
-$741万
-$19,089/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>D | 389呎 (2房)
-$735万
-$18,888/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>E | 393呎 (2房)
-$697万
-$17,734/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>F | 399呎 (2房)
-$707万
-$17,719/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>G | 398呎 (2房)
-$746万
-$18,756/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>H | 399呎 (2房)
-$698万
-$17,481/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="J26" s="21" t="inlineStr">
-        <is>
-          <t>J | 339呎 (2房)
-$650万
-$19,169/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="K26" s="21" t="inlineStr">
-        <is>
-          <t>K | 339呎 (2房)
-$661万
-$19,500/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="L26" s="21" t="inlineStr">
-        <is>
-          <t>L | 339呎 (2房)
-$654万
-$19,292/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="M26" s="21" t="inlineStr">
-        <is>
-          <t>M | 339呎 (2房)
-$654万
-$19,279/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>N | 339呎 (2房)
-$643万
-$18,968/呎
-(26年-05月-20日)</t>
-        </is>
-      </c>
-      <c r="O26" s="21" t="inlineStr">
-        <is>
-          <t>P | 343呎 (2房)
-$645万
-$18,797/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="P26" s="21" t="inlineStr">
-        <is>
-          <t>Q | 435呎 (2房)
-$864万
-$19,853/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-    </row>
     <row r="27" ht="58" customHeight="1">
       <c r="A27" s="19" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
           <t>A | 642呎 (3房)
 $1183万
 $18,427/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="C27" s="21" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>B | 390呎 (2房)
 $751万
 $19,255/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="D27" s="21" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>C | 388呎 (2房)
 $753万
 $19,415/呎
-(26年-04月-24日)</t>
+(26年-04月-25日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>D | 389呎 (2房)
 $730万
 $18,764/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -26157,7 +26157,7 @@
           <t>E | 393呎 (2房)
 $696万
 $17,700/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -26165,7 +26165,7 @@
           <t>F | 399呎 (2房)
 $706万
 $17,684/呎
-(26年-05月-18日)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -26173,7 +26173,7 @@
           <t>G | 398呎 (2房)
 $703万
 $17,660/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -26181,7 +26181,7 @@
           <t>H | 399呎 (2房)
 $693万
 $17,365/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="J27" s="21" t="inlineStr">
@@ -26189,7 +26189,7 @@
           <t>J | 339呎 (2房)
 $678万
 $19,996/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K27" s="21" t="inlineStr">
@@ -26197,7 +26197,7 @@
           <t>K | 339呎 (2房)
 $641万
 $18,919/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="L27" s="21" t="inlineStr">
@@ -26205,7 +26205,7 @@
           <t>L | 339呎 (2房)
 $648万
 $19,129/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="M27" s="21" t="inlineStr">
@@ -26213,7 +26213,7 @@
           <t>M | 339呎 (2房)
 $648万
 $19,115/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N27" s="21" t="inlineStr">
@@ -26221,7 +26221,7 @@
           <t>N | 339呎 (2房)
 $673万
 $19,854/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O27" s="21" t="inlineStr">
@@ -26229,7 +26229,7 @@
           <t>P | 343呎 (2房)
 $657万
 $19,142/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P27" s="21" t="inlineStr">
@@ -26237,7 +26237,7 @@
           <t>Q | 435呎 (2房)
 $842万
 $19,355/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
           <t>J | 301呎 (2房)
 $714万
 $23,708/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="K28" s="21" t="inlineStr">
@@ -26324,7 +26324,7 @@
           <t>K | 301呎 (2房)
 $715万
 $23,742/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="L28" s="21" t="inlineStr">
@@ -26332,7 +26332,7 @@
           <t>L | 301呎 (2房)
 $705万
 $23,424/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="M28" s="21" t="inlineStr">
@@ -26340,7 +26340,7 @@
           <t>M | 301呎 (2房)
 $690万
 $22,907/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="N28" s="21" t="inlineStr">
@@ -26348,7 +26348,7 @@
           <t>N | 301呎 (2房)
 $687万
 $22,822/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="O28" s="21" t="inlineStr">
@@ -26356,7 +26356,7 @@
           <t>P | 306呎 (2房)
 $701万
 $22,922/呎
-(26年-05月-26日)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="P28" s="21" t="inlineStr">
@@ -26364,7 +26364,7 @@
           <t>Q | 435呎 (2房)
 $912万
 $20,956/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,17 +116,12 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -200,7 +195,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -259,13 +254,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -643,12 +635,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -757,7 +749,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -767,12 +759,12 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -782,12 +774,12 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -797,7 +789,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1625,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1643,12 +1635,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1658,12 +1650,12 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1673,7 +1665,7 @@
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -9586,10 +9578,10 @@
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>7997000</v>
+        <v>9074000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>20043</v>
+        <v>22742</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -9597,10 +9589,10 @@
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>7277270</v>
+        <v>8257340</v>
       </c>
       <c r="L145" s="5" t="n">
-        <v>18239</v>
+        <v>20695</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
@@ -10516,25 +10508,25 @@
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>7970000</v>
+        <v>79700008995000</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>19975</v>
+        <v>199749395977</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>7252700</v>
+        <v>72527008185400</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>18177</v>
+        <v>181771950339</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11446,10 +11438,10 @@
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>7928000</v>
+        <v>8909000</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>19870</v>
+        <v>22328</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
@@ -11457,10 +11449,10 @@
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>7214480</v>
+        <v>8107190</v>
       </c>
       <c r="L175" s="5" t="n">
-        <v>18081</v>
+        <v>20319</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
@@ -12376,10 +12368,10 @@
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>7911000</v>
+        <v>8852000</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>19827</v>
+        <v>22185</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -12387,10 +12379,10 @@
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>7199010</v>
+        <v>8055320</v>
       </c>
       <c r="L190" s="5" t="n">
-        <v>18043</v>
+        <v>20189</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
@@ -13306,10 +13298,10 @@
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>7884000</v>
+        <v>8782000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>19759</v>
+        <v>22010</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13317,10 +13309,10 @@
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>7174440</v>
+        <v>7991620</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>17981</v>
+        <v>20029</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -14236,10 +14228,10 @@
         </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>7855000</v>
+        <v>8726000</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>19687</v>
+        <v>21870</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -14247,10 +14239,10 @@
         </is>
       </c>
       <c r="K220" s="5" t="n">
-        <v>7148050</v>
+        <v>7940660</v>
       </c>
       <c r="L220" s="5" t="n">
-        <v>17915</v>
+        <v>19901</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
@@ -15166,10 +15158,10 @@
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>7828000</v>
+        <v>8680000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>19619</v>
+        <v>21754</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
@@ -15177,10 +15169,10 @@
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>7123480</v>
+        <v>7898800</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>17853</v>
+        <v>19796</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
@@ -16096,10 +16088,10 @@
         </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>7806000</v>
+        <v>8640000</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>19564</v>
+        <v>21654</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16107,10 +16099,10 @@
         </is>
       </c>
       <c r="K250" s="5" t="n">
-        <v>7103460</v>
+        <v>7862400</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>17803</v>
+        <v>19705</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -17026,10 +17018,10 @@
         </is>
       </c>
       <c r="H265" s="5" t="n">
-        <v>7793000</v>
+        <v>8600000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>19531</v>
+        <v>21554</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
@@ -17037,10 +17029,10 @@
         </is>
       </c>
       <c r="K265" s="5" t="n">
-        <v>7091630</v>
+        <v>7826000</v>
       </c>
       <c r="L265" s="5" t="n">
-        <v>17774</v>
+        <v>19614</v>
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
@@ -17956,10 +17948,10 @@
         </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>7781000</v>
+        <v>8562000</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>19501</v>
+        <v>21459</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
@@ -17967,10 +17959,10 @@
         </is>
       </c>
       <c r="K280" s="5" t="n">
-        <v>7080710</v>
+        <v>7791420</v>
       </c>
       <c r="L280" s="5" t="n">
-        <v>17746</v>
+        <v>19527</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
@@ -18886,25 +18878,25 @@
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>7757000</v>
+        <v>77570008529000</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>19441</v>
+        <v>194411048945</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>9.00%</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>7058870</v>
+        <v>70588707761300</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>17691</v>
+        <v>176914054540</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>現金付款計劃 (減9.0%)</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -19816,10 +19808,10 @@
         </is>
       </c>
       <c r="H310" s="5" t="n">
-        <v>7724000</v>
+        <v>8484000</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>19358</v>
+        <v>21263</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
@@ -19827,10 +19819,10 @@
         </is>
       </c>
       <c r="K310" s="5" t="n">
-        <v>7028840</v>
+        <v>7720440</v>
       </c>
       <c r="L310" s="5" t="n">
-        <v>17616</v>
+        <v>19349</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
@@ -22597,7 +22589,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -22607,12 +22599,12 @@
       </c>
       <c r="H355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J355" s="3" t="inlineStr">
@@ -22622,12 +22614,12 @@
       </c>
       <c r="K355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L355" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M355" s="3" t="inlineStr">
@@ -22637,7 +22629,7 @@
       </c>
       <c r="N355" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22667,7 +22659,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -22677,12 +22669,12 @@
       </c>
       <c r="H356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J356" s="3" t="inlineStr">
@@ -22692,12 +22684,12 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M356" s="3" t="inlineStr">
@@ -22707,7 +22699,7 @@
       </c>
       <c r="N356" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22737,7 +22729,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -22747,12 +22739,12 @@
       </c>
       <c r="H357" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I357" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J357" s="3" t="inlineStr">
@@ -22762,12 +22754,12 @@
       </c>
       <c r="K357" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L357" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M357" s="3" t="inlineStr">
@@ -22777,7 +22769,7 @@
       </c>
       <c r="N357" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22807,7 +22799,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -22817,12 +22809,12 @@
       </c>
       <c r="H358" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I358" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J358" s="3" t="inlineStr">
@@ -22832,12 +22824,12 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M358" s="3" t="inlineStr">
@@ -22847,7 +22839,7 @@
       </c>
       <c r="N358" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22877,7 +22869,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -22887,12 +22879,12 @@
       </c>
       <c r="H359" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I359" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J359" s="3" t="inlineStr">
@@ -22902,12 +22894,12 @@
       </c>
       <c r="K359" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L359" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M359" s="3" t="inlineStr">
@@ -22917,7 +22909,7 @@
       </c>
       <c r="N359" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -22947,7 +22939,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -22957,12 +22949,12 @@
       </c>
       <c r="H360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J360" s="3" t="inlineStr">
@@ -22972,12 +22964,12 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M360" s="3" t="inlineStr">
@@ -22987,7 +22979,7 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23017,7 +23009,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -23027,12 +23019,12 @@
       </c>
       <c r="H361" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I361" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J361" s="3" t="inlineStr">
@@ -23042,12 +23034,12 @@
       </c>
       <c r="K361" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L361" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M361" s="3" t="inlineStr">
@@ -23057,7 +23049,7 @@
       </c>
       <c r="N361" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23087,7 +23079,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -23097,12 +23089,12 @@
       </c>
       <c r="H362" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I362" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J362" s="3" t="inlineStr">
@@ -23112,12 +23104,12 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M362" s="3" t="inlineStr">
@@ -23127,7 +23119,7 @@
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -23219,7 +23211,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -23234,7 +23226,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -23329,9 +23321,9 @@
       <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -23441,9 +23433,9 @@
       <c r="P5" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
+招标单位
 -
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -24525,11 +24517,11 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$800万
-$20,043/呎
+$907万
+$22,742/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -24652,11 +24644,11 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$797万
-$19,975/呎
+$7970000900万
+$199,749,395,977/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -24779,11 +24771,11 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$793万
-$19,870/呎
+$891万
+$22,328/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -24906,11 +24898,11 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I17" s="22" t="inlineStr">
+      <c r="I17" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$791万
-$19,827/呎
+$885万
+$22,185/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25033,11 +25025,11 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$788万
-$19,759/呎
+$878万
+$22,010/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25160,11 +25152,11 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$786万
-$19,687/呎
+$873万
+$21,870/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25287,11 +25279,11 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I20" s="22" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$783万
-$19,619/呎
+$868万
+$21,754/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25414,11 +25406,11 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I21" s="22" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$781万
-$19,564/呎
+$864万
+$21,654/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25541,11 +25533,11 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$779万
-$19,531/呎
+$860万
+$21,554/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25668,11 +25660,11 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$778万
-$19,501/呎
+$856万
+$21,459/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25795,11 +25787,11 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I24" s="22" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$776万
-$19,441/呎
+$7757000853万
+$194,411,048,945/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -25922,11 +25914,11 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="22" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$772万
-$19,358/呎
+$848万
+$21,263/呎
 (已定价未售)</t>
         </is>
       </c>
@@ -26250,65 +26242,65 @@
       <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 605呎 (3房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 352呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 352呎 (2房)
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>C | 350呎 (2房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 352呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>C | 350呎 (2房)
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 355呎 (2房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 362呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 352呎 (2房)
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 360呎 (2房)
+招标单位
 -
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I28" s="20" t="inlineStr">
+        <is>
+          <t>H | 361呎 (2房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 355呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 362呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 360呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
-        <is>
-          <t>H | 361呎 (2房)
--
--
-(待售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -124,6 +124,12 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -195,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -258,6 +264,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -749,7 +758,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1625,7 +1634,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -22589,7 +22598,7 @@
       </c>
       <c r="F355" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G355" s="3" t="inlineStr">
@@ -22659,7 +22668,7 @@
       </c>
       <c r="F356" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G356" s="3" t="inlineStr">
@@ -22729,7 +22738,7 @@
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G357" s="3" t="inlineStr">
@@ -22799,7 +22808,7 @@
       </c>
       <c r="F358" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G358" s="3" t="inlineStr">
@@ -22869,7 +22878,7 @@
       </c>
       <c r="F359" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G359" s="3" t="inlineStr">
@@ -22939,7 +22948,7 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
@@ -23009,7 +23018,7 @@
       </c>
       <c r="F361" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G361" s="3" t="inlineStr">
@@ -23079,7 +23088,7 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
@@ -23318,12 +23327,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr">
@@ -23430,12 +23439,12 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P5" s="20" t="inlineStr">
+      <c r="P5" s="22" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -26239,68 +26248,68 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 605呎 (3房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 352呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
         <is>
           <t>D | 352呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
         <is>
           <t>E | 355呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
         <is>
           <t>F | 362呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
         <is>
           <t>G | 360呎 (2房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I28" s="20" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 361呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J28" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -116,18 +116,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00660000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -201,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -260,13 +255,10 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -8219,14 +8211,14 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
-        <v>8851500</v>
+        <v>9046100</v>
       </c>
       <c r="I123" s="5" t="n">
-        <v>20348</v>
+        <v>20796</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -8234,10 +8226,10 @@
         </is>
       </c>
       <c r="K123" s="5" t="n">
-        <v>8851500</v>
+        <v>9046100</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>20348</v>
+        <v>20796</v>
       </c>
       <c r="M123" s="3" t="inlineStr">
         <is>
@@ -9578,7 +9570,7 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
@@ -10508,7 +10500,7 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
@@ -11438,7 +11430,7 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
@@ -12368,7 +12360,7 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
@@ -13298,7 +13290,7 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
@@ -14228,7 +14220,7 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
@@ -15158,7 +15150,7 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
@@ -16088,7 +16080,7 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
@@ -17018,7 +17010,7 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
@@ -17948,7 +17940,7 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
@@ -18878,7 +18870,7 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
@@ -19808,7 +19800,7 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
@@ -23215,12 +23207,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>22</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -23327,7 +23319,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 642呎 (3房)
 招标单位
@@ -23439,7 +23431,7 @@
 (26年-05月-27日)</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr">
+      <c r="P5" s="20" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
 招标单位
@@ -24458,9 +24450,9 @@
       <c r="P13" s="21" t="inlineStr">
         <is>
           <t>Q | 435呎 (2房)
-$885万
-$20,348/呎
-(26年-05月-21日)</t>
+$905万
+$20,796/呎
+(26年-04月-30日)</t>
         </is>
       </c>
     </row>
@@ -24531,7 +24523,7 @@
           <t>H | 399呎 (2房)
 $907万
 $22,742/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -24658,7 +24650,7 @@
           <t>H | 399呎 (2房)
 $7970000900万
 $199,749,395,977/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -24785,7 +24777,7 @@
           <t>H | 399呎 (2房)
 $891万
 $22,328/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -24912,7 +24904,7 @@
           <t>H | 399呎 (2房)
 $885万
 $22,185/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -25039,7 +25031,7 @@
           <t>H | 399呎 (2房)
 $878万
 $22,010/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -25166,7 +25158,7 @@
           <t>H | 399呎 (2房)
 $873万
 $21,870/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">
@@ -25293,7 +25285,7 @@
           <t>H | 399呎 (2房)
 $868万
 $21,754/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -25420,7 +25412,7 @@
           <t>H | 399呎 (2房)
 $864万
 $21,654/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -25547,7 +25539,7 @@
           <t>H | 399呎 (2房)
 $860万
 $21,554/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -25674,7 +25666,7 @@
           <t>H | 399呎 (2房)
 $856万
 $21,459/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -25801,7 +25793,7 @@
           <t>H | 399呎 (2房)
 $7757000853万
 $194,411,048,945/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -25928,7 +25920,7 @@
           <t>H | 399呎 (2房)
 $848万
 $21,263/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">
@@ -26248,7 +26240,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 605呎 (3房)
 招标单位
@@ -26256,7 +26248,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 352呎 (2房)
 招标单位
@@ -26264,7 +26256,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
 招标单位
@@ -26272,7 +26264,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>D | 352呎 (2房)
 招标单位
@@ -26280,7 +26272,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>E | 355呎 (2房)
 招标单位
@@ -26288,7 +26280,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="20" t="inlineStr">
         <is>
           <t>F | 362呎 (2房)
 招标单位
@@ -26296,7 +26288,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H28" s="22" t="inlineStr">
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>G | 360呎 (2房)
 招标单位
@@ -26304,7 +26296,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I28" s="22" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>H | 361呎 (2房)
 招标单位

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -22940,38 +22940,30 @@
       </c>
       <c r="F360" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H360" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I360" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="H360" s="5" t="n">
+        <v>8470000</v>
+      </c>
+      <c r="I360" s="5" t="n">
+        <v>24200</v>
       </c>
       <c r="J360" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K360" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L360" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K360" s="5" t="n">
+        <v>8470000</v>
+      </c>
+      <c r="L360" s="5" t="n">
+        <v>24200</v>
       </c>
       <c r="M360" s="3" t="inlineStr">
         <is>
@@ -22980,7 +22972,7 @@
       </c>
       <c r="N360" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23207,7 +23199,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23217,7 +23209,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>338</t>
+          <t>339</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26256,12 +26248,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 350呎 (2房)
-招标单位
--
-(在售)</t>
+$847万
+$24,200/呎
+(26年-08月-13日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -15150,34 +15150,34 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>8680000</v>
+        <v>8332800</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>21754</v>
+        <v>20884</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>7898800</v>
+        <v>8332800</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>19796</v>
+        <v>20884</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -16080,23 +16080,23 @@
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
-        <v>8640000</v>
+        <v>7862400</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>21654</v>
+        <v>19705</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K250" s="5" t="n">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N250" s="3" t="inlineStr">
@@ -17010,23 +17010,23 @@
       </c>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
-        <v>8600000</v>
+        <v>7826000</v>
       </c>
       <c r="I265" s="5" t="n">
-        <v>21554</v>
+        <v>19614</v>
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K265" s="5" t="n">
@@ -17037,7 +17037,7 @@
       </c>
       <c r="M265" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N265" s="3" t="inlineStr">
@@ -17940,34 +17940,34 @@
       </c>
       <c r="F280" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
-        <v>8562000</v>
+        <v>7791400</v>
       </c>
       <c r="I280" s="5" t="n">
-        <v>21459</v>
+        <v>19527</v>
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K280" s="5" t="n">
-        <v>7791420</v>
+        <v>7791400</v>
       </c>
       <c r="L280" s="5" t="n">
         <v>19527</v>
       </c>
       <c r="M280" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N280" s="3" t="inlineStr">
@@ -18870,34 +18870,34 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>77570008529000</v>
+        <v>7761300</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>194411048945</v>
+        <v>19452</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>70588707761300</v>
+        <v>7761300</v>
       </c>
       <c r="L295" s="5" t="n">
-        <v>176914054540</v>
+        <v>19452</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -19800,34 +19800,34 @@
       </c>
       <c r="F310" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
-        <v>8484000</v>
+        <v>7720400</v>
       </c>
       <c r="I310" s="5" t="n">
-        <v>21263</v>
+        <v>19349</v>
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K310" s="5" t="n">
-        <v>7720440</v>
+        <v>7720400</v>
       </c>
       <c r="L310" s="5" t="n">
         <v>19349</v>
       </c>
       <c r="M310" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N310" s="3" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25272,12 +25272,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$868万
-$21,754/呎
-(在售)</t>
+$833万
+$20,884/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">
@@ -25399,12 +25399,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I21" s="20" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$864万
-$21,654/呎
-(在售)</t>
+$786万
+$19,705/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -25526,12 +25526,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I22" s="20" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$860万
-$21,554/呎
-(在售)</t>
+$783万
+$19,614/呎
+(26年-08月-15日)</t>
         </is>
       </c>
       <c r="J22" s="21" t="inlineStr">
@@ -25653,12 +25653,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I23" s="20" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$856万
-$21,459/呎
-(在售)</t>
+$779万
+$19,527/呎
+(26年-08月-15日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -25780,12 +25780,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I24" s="20" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$7757000853万
-$194,411,048,945/呎
-(在售)</t>
+$776万
+$19,452/呎
+(26年-08月-15日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
@@ -25907,12 +25907,12 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="I25" s="20" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$848万
-$21,263/呎
-(在售)</t>
+$772万
+$19,349/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="J25" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -636,12 +636,12 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -10500,34 +10500,34 @@
       </c>
       <c r="F160" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
-        <v>79700008995000</v>
+        <v>8185400</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>199749395977</v>
+        <v>20515</v>
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>9.00%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K160" s="5" t="n">
-        <v>72527008185400</v>
+        <v>8185400</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>181771950339</v>
+        <v>20515</v>
       </c>
       <c r="M160" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減9.0%)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N160" s="3" t="inlineStr">
@@ -11430,34 +11430,34 @@
       </c>
       <c r="F175" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
-        <v>8909000</v>
+        <v>8107100</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>22328</v>
+        <v>20319</v>
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K175" s="5" t="n">
-        <v>8107190</v>
+        <v>8107100</v>
       </c>
       <c r="L175" s="5" t="n">
         <v>20319</v>
       </c>
       <c r="M175" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N175" s="3" t="inlineStr">
@@ -12360,34 +12360,34 @@
       </c>
       <c r="F190" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
-        <v>8852000</v>
+        <v>8055300</v>
       </c>
       <c r="I190" s="5" t="n">
-        <v>22185</v>
+        <v>20189</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K190" s="5" t="n">
-        <v>8055320</v>
+        <v>8055300</v>
       </c>
       <c r="L190" s="5" t="n">
         <v>20189</v>
       </c>
       <c r="M190" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N190" s="3" t="inlineStr">
@@ -13290,34 +13290,34 @@
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
-        <v>8782000</v>
+        <v>8430700</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>22010</v>
+        <v>21130</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K205" s="5" t="n">
-        <v>7991620</v>
+        <v>8430700</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>20029</v>
+        <v>21130</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N205" s="3" t="inlineStr">
@@ -14220,34 +14220,34 @@
       </c>
       <c r="F220" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>8726000</v>
+        <v>7940600</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>21870</v>
+        <v>19901</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K220" s="5" t="n">
-        <v>7940660</v>
+        <v>7940600</v>
       </c>
       <c r="L220" s="5" t="n">
         <v>19901</v>
       </c>
       <c r="M220" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N220" s="3" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24637,12 +24637,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I15" s="20" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$7970000900万
-$199,749,395,977/呎
-(在售)</t>
+$819万
+$20,515/呎
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr">
@@ -24764,12 +24764,12 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="I16" s="20" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$891万
-$22,328/呎
-(在售)</t>
+$811万
+$20,319/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -24891,12 +24891,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I17" s="20" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$885万
-$22,185/呎
-(在售)</t>
+$806万
+$20,189/呎
+(26年-08月-18日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr">
@@ -25018,12 +25018,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$878万
-$22,010/呎
-(在售)</t>
+$843万
+$21,130/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr">
@@ -25145,12 +25145,12 @@
 (26年-04月-25日)</t>
         </is>
       </c>
-      <c r="I19" s="20" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$873万
-$21,870/呎
-(在售)</t>
+$794万
+$19,901/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -15150,34 +15150,34 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>已售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>8332800</v>
+        <v>8680000</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>20884</v>
+        <v>21754</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
-        <v>8332800</v>
+        <v>7898800</v>
       </c>
       <c r="L235" s="5" t="n">
-        <v>20884</v>
+        <v>19796</v>
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>100天付款計劃</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -23199,7 +23199,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23209,7 +23209,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>349</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25272,12 +25272,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$833万
-$20,884/呎
-(26年-08月-16日)</t>
+$868万
+$21,754/呎
+(在售)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -23072,38 +23072,30 @@
       </c>
       <c r="F362" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H362" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I362" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H362" s="5" t="n">
+        <v>16335000</v>
+      </c>
+      <c r="I362" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="J362" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K362" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L362" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K362" s="5" t="n">
+        <v>16335000</v>
+      </c>
+      <c r="L362" s="5" t="n">
+        <v>27000</v>
       </c>
       <c r="M362" s="3" t="inlineStr">
         <is>
@@ -23112,7 +23104,7 @@
       </c>
       <c r="N362" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -23199,7 +23191,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23209,7 +23201,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>350</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -26232,12 +26224,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>A | 605呎 (3房)
-招标单位
--
-(在售)</t>
+$1634万
+$27,000/呎
+(26年-08月-27日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -15150,23 +15150,23 @@
       </c>
       <c r="F235" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
-        <v>8680000</v>
+        <v>7898800</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>21754</v>
+        <v>19796</v>
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K235" s="5" t="n">
@@ -15177,7 +15177,7 @@
       </c>
       <c r="M235" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N235" s="3" t="inlineStr">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>351</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -25264,12 +25264,12 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="I20" s="20" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$868万
-$21,754/呎
-(在售)</t>
+$790万
+$19,796/呎
+(26年-08月-29日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -9570,34 +9570,34 @@
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
-        <v>9074000</v>
+        <v>8257300</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>22742</v>
+        <v>20695</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K145" s="5" t="n">
-        <v>8257340</v>
+        <v>8257300</v>
       </c>
       <c r="L145" s="5" t="n">
         <v>20695</v>
       </c>
       <c r="M145" s="3" t="inlineStr">
         <is>
-          <t>100天付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N145" s="3" t="inlineStr">
@@ -16085,7 +16085,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -17945,7 +17945,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -22945,7 +22945,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23191,7 +23191,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -23201,7 +23201,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>352</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -24502,12 +24502,12 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 399呎 (2房)
-$907万
-$22,742/呎
-(在售)</t>
+$826万
+$20,695/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr">
@@ -25396,7 +25396,7 @@
           <t>H | 399呎 (2房)
 $786万
 $19,705/呎
-(26年-08月-16日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr">
@@ -25650,7 +25650,7 @@
           <t>H | 399呎 (2房)
 $779万
 $19,527/呎
-(26年-08月-15日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="J23" s="21" t="inlineStr">
@@ -26245,7 +26245,7 @@
           <t>C | 350呎 (2房)
 $847万
 $24,200/呎
-(26年-08月-13日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">

--- a/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
+++ b/九龙-红磡-首岸第1期/首岸第1期_销控明细表.xlsx
@@ -11435,7 +11435,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -24761,7 +24761,7 @@
           <t>H | 399呎 (2房)
 $811万
 $20,319/呎
-(26年-08月-18日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr">
@@ -25777,7 +25777,7 @@
           <t>H | 399呎 (2房)
 $776万
 $19,452/呎
-(26年-08月-15日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="J24" s="21" t="inlineStr">
